--- a/TESTS/zlit_5_kapelukh.xlsx
+++ b/TESTS/zlit_5_kapelukh.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -561,6 +561,11 @@
           <t>Тип</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ГР</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -580,7 +585,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Туве Янссон — фінська письменниця і художниця що створила світ Мумі-тролів</t>
+          <t>Туве Янссон</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -601,6 +606,11 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -622,7 +632,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Фінляндія — хоча Янссон писала шведською мовою вона є фінською авторкою</t>
+          <t>Фінляндія</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -643,6 +653,11 @@
       <c r="H3" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -664,7 +679,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Серії книг про Мумі-тролів — Янссон створила цілий казковий світ Долини Мумі-тролів</t>
+          <t>Серії книг про Мумі-тролів</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -685,6 +700,11 @@
       <c r="H4" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -706,7 +726,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Мумі-троль — добрий і допитливий мешканець казкової долини</t>
+          <t>Мумі-троль</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -727,6 +747,11 @@
       <c r="H5" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -748,7 +773,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Добрим допитливим і відкритим до пригод — він любить друзів і не боїться нового</t>
+          <t>Добрим допитливим і відкритим до пригод</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -769,6 +794,11 @@
       <c r="H6" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -790,7 +820,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Незвичайний чорний капелюх що знайшов Мумі-троль — він виявився чарівним і почав перетворювати речі</t>
+          <t>Незвичайний чорний капелюх що знайшов Мумі-троль</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -811,6 +841,11 @@
       <c r="H7" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -832,7 +867,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Перетворював — хмари ставали кущами яєчка — маленькими хмарками сам Мумі-троль змінив вигляд</t>
+          <t>Перетворював</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -853,6 +888,11 @@
       <c r="H8" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -874,7 +914,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Він перетворився так що рідна мама не впізнала його — це дуже засмутило всіх</t>
+          <t>Він перетворився так що рідна мама не впізнала його</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -895,6 +935,11 @@
       <c r="H9" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -916,7 +961,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Мама впізнала його серцем і від її сліз він повернув справжнє обличчя — любов сильніша за магію</t>
+          <t>Мама впізнала його серцем і від її сліз він повернув справжнє обличчя</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -937,6 +982,11 @@
       <c r="H10" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -948,37 +998,42 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 1)</t>
+          <t>Де живе родина Мумі-тролів?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>У великому місті</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>У затишному будиночку в Мумі-долині, біля річки</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>У замку на горі</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>На кораблі</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -990,37 +1045,42 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 2)</t>
+          <t>Якою є атмосфера в домі Мумі-тролів, описана в книзі?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Сувора і тиха</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Тепла, гостинна — двері завжди відчинені для друзів і навіть незнайомців</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Сумна і самотня</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Напружена і ворожа</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1032,37 +1092,42 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 3)</t>
+          <t>Хто з родини Мумі-тролів найбільше любить читати книжки про пригоди й мрії про море?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Мама Мумі-троля</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Тато Мумі-троля</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Сам Мумі-троль</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Чарівник</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1074,37 +1139,42 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 1)</t>
+          <t>Що сталося, коли в чарівний капелюх поклали яєчні шкаралупки?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Нічого</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Із них з'явились маленькі хмаринки, що поплили по кімнаті</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Вони зникли</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Вони перетворились на каміння</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1116,37 +1186,42 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 2)</t>
+          <t>Що сталося, коли капелюх наповнили водою?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Вода просто витекла</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Вода в капелюсі набула властивостей чарівного джерела</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Капелюх потонув</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Капелюх змінив колір</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1158,37 +1233,42 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 3)</t>
+          <t>Як друзі зрозуміли, що капелюх саме чарівний, а не просто дивний?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Прочитали написи на ньому</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Помітили, що будь-яка звичайна річ, покладена в нього, перетворюється на щось інше</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Чарівник сам розповів</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Капелюх засвітився</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1200,37 +1280,42 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 1)</t>
+          <t>Кому насправді належав загублений чорний капелюх?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Хемулю</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Чарівнику, що подорожує на чорній пантері і шукає свій коштовний камінь</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Снусмумрику</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Морському королю</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1242,37 +1327,42 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 2)</t>
+          <t>Що шукав Чарівник у Долині Мумі-тролів?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Свій капелюх і втрачений чарівний рубін</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Нову домівку</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Друзів</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Їжу</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1284,37 +1374,42 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 3)</t>
+          <t>Як мешканці Долини спершу реагували на появу Чарівника?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Зустріли його з радістю одразу</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Трохи побоювалися його, адже не знали, чого від нього чекати</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Прогнали його</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Не помітили його</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1326,37 +1421,42 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 1)</t>
+          <t>Що сталося, коли в капелюх насипали звичайний пісок?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Пісок просто залишився піском</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Пісок перетворився на хмари, на яких можна було літати</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Пісок зник</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Пісок став золотом</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1368,37 +1468,42 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 2)</t>
+          <t>Що друзі зробили, опанувавши хмари з капелюха?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Залишили їх удома</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Полетіли на хмарах у мандрівку над Долиною</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Продали їх</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Сховали від усіх</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1410,37 +1515,42 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 3)</t>
+          <t>Чим небезпечні виявились забавки з капелюхом, попри всю радість?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Нічим, усе було безпечно</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Перетворення були непередбачувані, і не всі речі варто було туди класти</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Капелюх міг вибухнути</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Капелюх крався</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1452,37 +1562,42 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 1)</t>
+          <t>Чому Мумі-троль заліз у капелюх під час гри в хованки?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Йому наказали</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Він шукав найкраще місце, щоб сховатися від друзів</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він хотів випробувати капелюх свідомо</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Йому стало цікаво, що там усередині</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1494,37 +1609,42 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 2)</t>
+          <t>На кого перетворився Мумі-троль, вилізши з капелюха?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>На Чарівника</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>На дивну, незнайому істоту з великими очима, яку ніхто не впізнав</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>На хмару</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>На камінь</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1536,37 +1656,42 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 3)</t>
+          <t>Як реагували друзі на нову, незнайому істоту, що вийшла з капелюха?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Одразу впізнали Мумі-троля</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Налякались і не впізнали в ній свого друга</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Розсміялись</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Привітали як гостя</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1578,37 +1703,42 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 1)</t>
+          <t>Що відчував «новий» Мумі-троль, коли його не впізнавали навіть найближчі друзі?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Радість</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Самотність і відчай — він залишався собою всередині, але ніхто цього не бачив</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Байдужість</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Гордість новим вигля­дом</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1620,37 +1750,42 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 2)</t>
+          <t>Хто єдиний відчув, що дивна істота — це насправді Мумі-троль?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Тато Мумі-троля</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Мама Мумі-троля, яка впізнала його серцем, незважаючи на новий вигляд</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Снусмумрик</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Чарівник</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1662,37 +1797,42 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 3)</t>
+          <t>Що саме повернуло Мумі-тролю його справжній вигляд?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Заклинання Чарівника</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Сльози і люблячий погляд мами, яка впізнала його, попри все</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Новий стрибок у капелюх</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Зняття капелюха з голови</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1704,37 +1844,42 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 1)</t>
+          <t>Де врешті знайшовся загублений рубін Чарівника?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>У капелюсі</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>У Хемуля, який знайшов і тримав його як звичайний камінець</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>У річці</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>У кишені Мумі-троля</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1746,37 +1891,42 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 2)</t>
+          <t>Як Чарівник віддячив мешканцям Долини за повернення рубіна?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Нічим не віддячив</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Виконав бажання друзів і подарував їм радісне свято</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Забрав капелюх назавжди</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Покарав їх</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1788,37 +1938,42 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 3)</t>
+          <t>Чим закінчується історія для самого чарівного капелюха?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Його знищують</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Він залишається в домі Мумі-тролів як незвичайний, але вже знайомий предмет</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Чарівник забирає його назавжди</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Його викидають у річку</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1843,8 +1998,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>А</t>
@@ -1853,6 +2006,11 @@
       <c r="H32" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1877,8 +2035,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>А</t>
@@ -1887,6 +2043,11 @@
       <c r="H33" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1911,8 +2072,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>А</t>
@@ -1921,6 +2080,11 @@
       <c r="H34" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1932,21 +2096,19 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Що символізує капелюх у книзі?</t>
+          <t>Чарівний капелюх символізує те, як легко все навколо може несподівано змінитися.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>А</t>
@@ -1955,6 +2117,11 @@
       <c r="H35" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1966,21 +2133,19 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Яка атмосфера характерна для книг Туве Янссон про Мумі-тролів?</t>
+          <t>Для книг Туве Янссон про Мумі-тролів характерна тепла, затишна і водночас трохи дивакувата атмосфера.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>А</t>
@@ -1989,6 +2154,11 @@
       <c r="H36" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2000,21 +2170,19 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Яку роль відіграє сім'я Мумі-тролів у всіх книгах серії?</t>
+          <t>У всіх книгах серії про Мумі-тролів сім'я та дім є місцем, куди завжди можна повернутися.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
           <t>А</t>
@@ -2023,6 +2191,11 @@
       <c r="H37" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2034,21 +2207,19 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Хто такий Чарівник і що він шукав у Долині Мумі-тролів?</t>
+          <t>Чарівник у книзі шукав свій загублений капелюх і коштовний рубін.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>А</t>
@@ -2057,6 +2228,11 @@
       <c r="H38" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2068,29 +2244,32 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Яка нагорода чекала жителів долини від Чарівника в кінці книги?</t>
+          <t>Наприкінці книги Чарівник так і не знайшов те, що шукав, і пішов розчарованим.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2102,21 +2281,19 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Яка головна ідея книги «Капелюх Чарівника»?</t>
+          <t>Головна ідея книги — навіть незвичайне й лякаюче спочатку може стати приводом для дружби і радості.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
           <t>А</t>
@@ -2125,6 +2302,11 @@
       <c r="H40" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2169,6 +2351,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2211,6 +2398,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2220,27 +2412,27 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Які теми розкриває «Капелюх Чарівника»?</t>
+          <t>Що відбувалося з різними речами, покладеними у чарівний капелюх?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Сила сімейної любові</t>
+          <t>Яєчні шкаралупки ставали хмарами</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Прийняття незвичайного і нового</t>
+          <t>Мумі-троль перетворився на незнайому істоту</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Небезпека магії</t>
+          <t>Капелюх зникав назавжди</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Цінність дружби</t>
+          <t>Пісок перетворювався на хмари</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2251,6 +2443,11 @@
       <c r="H43" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2469,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Найкращий друг Мумі-троля — вільний мрійник що грає на флейті і цінує самотність і природу</t>
+          <t>Найкращий друг Мумі-троля</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2293,6 +2490,11 @@
       <c r="H44" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2337,6 +2539,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2356,7 +2563,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Тривожна і метушлива сусідка — символ надмірної серйозності і страху перед незвичайним</t>
+          <t>Тривожна і метушлива сусідка</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2377,6 +2584,11 @@
       <c r="H46" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
